--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,6 +937,218 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122748148</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91598</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>366</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storflobodarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566414</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6515480</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122748147</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90400</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>937</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vit vedfingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lentaria epichnoa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storflobodarna V, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566417</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6515477</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>122748148</v>
       </c>
       <c r="B4" t="n">
-        <v>91598</v>
+        <v>91701</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>122748147</v>
       </c>
       <c r="B5" t="n">
-        <v>90400</v>
+        <v>90503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>122748148</v>
       </c>
       <c r="B4" t="n">
-        <v>91701</v>
+        <v>91705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>122748147</v>
       </c>
       <c r="B5" t="n">
-        <v>90503</v>
+        <v>90507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748148</v>
+        <v>122748147</v>
       </c>
       <c r="B4" t="n">
-        <v>91705</v>
+        <v>90507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>366</v>
+        <v>937</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566414</v>
+        <v>566417</v>
       </c>
       <c r="R4" t="n">
-        <v>6515480</v>
+        <v>6515477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748147</v>
+        <v>122748148</v>
       </c>
       <c r="B5" t="n">
-        <v>90507</v>
+        <v>91705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>937</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566417</v>
+        <v>566414</v>
       </c>
       <c r="R5" t="n">
-        <v>6515477</v>
+        <v>6515480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>122748147</v>
       </c>
       <c r="B4" t="n">
-        <v>90507</v>
+        <v>90515</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>122748148</v>
       </c>
       <c r="B5" t="n">
-        <v>91705</v>
+        <v>91713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748147</v>
+        <v>122748148</v>
       </c>
       <c r="B4" t="n">
-        <v>90515</v>
+        <v>91713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>937</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566417</v>
+        <v>566414</v>
       </c>
       <c r="R4" t="n">
-        <v>6515477</v>
+        <v>6515480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748148</v>
+        <v>122748147</v>
       </c>
       <c r="B5" t="n">
-        <v>91713</v>
+        <v>90515</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>366</v>
+        <v>937</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566414</v>
+        <v>566417</v>
       </c>
       <c r="R5" t="n">
-        <v>6515480</v>
+        <v>6515477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748148</v>
+        <v>122748147</v>
       </c>
       <c r="B4" t="n">
-        <v>91713</v>
+        <v>90515</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>366</v>
+        <v>937</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566414</v>
+        <v>566417</v>
       </c>
       <c r="R4" t="n">
-        <v>6515480</v>
+        <v>6515477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748147</v>
+        <v>122748148</v>
       </c>
       <c r="B5" t="n">
-        <v>90515</v>
+        <v>91713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>937</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566417</v>
+        <v>566414</v>
       </c>
       <c r="R5" t="n">
-        <v>6515477</v>
+        <v>6515480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>122748147</v>
       </c>
       <c r="B4" t="n">
-        <v>90515</v>
+        <v>90518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>122748148</v>
       </c>
       <c r="B5" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>122748147</v>
       </c>
       <c r="B4" t="n">
-        <v>90518</v>
+        <v>90520</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>122748148</v>
       </c>
       <c r="B5" t="n">
-        <v>91716</v>
+        <v>91718</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -675,69 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92746900</v>
+        <v>122748148</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bogestad SV 385 m, Ög</t>
+          <t>Storflobodarna V, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566259.5593713383</v>
+        <v>566414</v>
       </c>
       <c r="R2" t="n">
-        <v>6515487.994697209</v>
+        <v>6515480</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,44 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Förefaller vara en 40-årig "granåker"</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106461973</v>
+        <v>122748147</v>
       </c>
       <c r="B3" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,45 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>937</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bogestad, Simonstorp, Ög</t>
+          <t>Storflobodarna V, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566321.0695247211</v>
+        <v>566417</v>
       </c>
       <c r="R3" t="n">
-        <v>6515506.68099835</v>
+        <v>6515477</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,27 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>RVNO inv</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,65 +861,67 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Svensson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Svensson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122748147</v>
+        <v>131493353</v>
       </c>
       <c r="B4" t="n">
-        <v>90520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>937</v>
+        <v>1965</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Citronporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Antrodiella citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>Niemelä &amp; Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storflobodarna V, Ög</t>
+          <t>Bogestad, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566417</v>
+        <v>566514</v>
       </c>
       <c r="R4" t="n">
-        <v>6515477</v>
+        <v>6515489</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,12 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,75 +959,83 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122748148</v>
+        <v>92746900</v>
       </c>
       <c r="B5" t="n">
-        <v>91718</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>366</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storflobodarna V, Ög</t>
+          <t>Bogestad SV 385 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566414</v>
+        <v>566260</v>
       </c>
       <c r="R5" t="n">
-        <v>6515480</v>
+        <v>6515488</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2021-04-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2021-04-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,25 +1073,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Förefaller vara en 40-årig "granåker"</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122748148</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122748147</t>
         </is>
       </c>
     </row>
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131493353</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,8 +1119,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92746900</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>